--- a/modelo_op_solda.xlsx
+++ b/modelo_op_solda.xlsx
@@ -3,8 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Página1" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="OP" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="OP" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -494,7 +493,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="53">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -578,12 +577,6 @@
     <xf borderId="27" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="27" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="27" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
     <xf borderId="27" fillId="3" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
@@ -629,10 +622,6 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -862,17 +851,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
-  <sheetData/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1350,7 +1328,7 @@
       <c r="AE8" s="38"/>
       <c r="AF8" s="38"/>
       <c r="AG8" s="39"/>
-      <c r="AH8" s="41" t="s">
+      <c r="AH8" s="40" t="s">
         <v>11</v>
       </c>
       <c r="AI8" s="38"/>
@@ -1360,7 +1338,7 @@
         <v>12</v>
       </c>
       <c r="AM8" s="39"/>
-      <c r="AN8" s="42" t="s">
+      <c r="AN8" s="37" t="s">
         <v>13</v>
       </c>
       <c r="AO8" s="39"/>
@@ -1378,12 +1356,12 @@
     </row>
     <row r="9" ht="25.5" customHeight="1">
       <c r="A9" s="9"/>
-      <c r="B9" s="43"/>
+      <c r="B9" s="41"/>
       <c r="C9" s="38"/>
       <c r="D9" s="38"/>
       <c r="E9" s="38"/>
       <c r="F9" s="39"/>
-      <c r="G9" s="44"/>
+      <c r="G9" s="42"/>
       <c r="H9" s="38"/>
       <c r="I9" s="38"/>
       <c r="J9" s="38"/>
@@ -1400,25 +1378,25 @@
       <c r="U9" s="38"/>
       <c r="V9" s="38"/>
       <c r="W9" s="39"/>
-      <c r="X9" s="44"/>
+      <c r="X9" s="42"/>
       <c r="Y9" s="38"/>
       <c r="Z9" s="38"/>
       <c r="AA9" s="38"/>
       <c r="AB9" s="38"/>
       <c r="AC9" s="39"/>
-      <c r="AD9" s="45"/>
+      <c r="AD9" s="43"/>
       <c r="AE9" s="38"/>
       <c r="AF9" s="38"/>
       <c r="AG9" s="39"/>
-      <c r="AH9" s="46" t="s">
+      <c r="AH9" s="44" t="s">
         <v>14</v>
       </c>
       <c r="AI9" s="38"/>
       <c r="AJ9" s="38"/>
       <c r="AK9" s="39"/>
-      <c r="AL9" s="45"/>
+      <c r="AL9" s="43"/>
       <c r="AM9" s="39"/>
-      <c r="AN9" s="46" t="s">
+      <c r="AN9" s="44" t="s">
         <v>14</v>
       </c>
       <c r="AO9" s="39"/>
@@ -1436,12 +1414,12 @@
     </row>
     <row r="10" ht="25.5" customHeight="1">
       <c r="A10" s="9"/>
-      <c r="B10" s="43"/>
+      <c r="B10" s="41"/>
       <c r="C10" s="38"/>
       <c r="D10" s="38"/>
       <c r="E10" s="38"/>
       <c r="F10" s="39"/>
-      <c r="G10" s="47"/>
+      <c r="G10" s="45"/>
       <c r="H10" s="38"/>
       <c r="I10" s="38"/>
       <c r="J10" s="38"/>
@@ -1458,25 +1436,25 @@
       <c r="U10" s="38"/>
       <c r="V10" s="38"/>
       <c r="W10" s="39"/>
-      <c r="X10" s="44"/>
+      <c r="X10" s="42"/>
       <c r="Y10" s="38"/>
       <c r="Z10" s="38"/>
       <c r="AA10" s="38"/>
       <c r="AB10" s="38"/>
       <c r="AC10" s="39"/>
-      <c r="AD10" s="45"/>
+      <c r="AD10" s="43"/>
       <c r="AE10" s="38"/>
       <c r="AF10" s="38"/>
       <c r="AG10" s="39"/>
-      <c r="AH10" s="46" t="s">
+      <c r="AH10" s="44" t="s">
         <v>14</v>
       </c>
       <c r="AI10" s="38"/>
       <c r="AJ10" s="38"/>
       <c r="AK10" s="39"/>
-      <c r="AL10" s="45"/>
+      <c r="AL10" s="43"/>
       <c r="AM10" s="39"/>
-      <c r="AN10" s="46" t="s">
+      <c r="AN10" s="44" t="s">
         <v>14</v>
       </c>
       <c r="AO10" s="39"/>
@@ -1494,12 +1472,12 @@
     </row>
     <row r="11" ht="25.5" customHeight="1">
       <c r="A11" s="9"/>
-      <c r="B11" s="43"/>
+      <c r="B11" s="41"/>
       <c r="C11" s="38"/>
       <c r="D11" s="38"/>
       <c r="E11" s="38"/>
       <c r="F11" s="39"/>
-      <c r="G11" s="47"/>
+      <c r="G11" s="45"/>
       <c r="H11" s="38"/>
       <c r="I11" s="38"/>
       <c r="J11" s="38"/>
@@ -1516,25 +1494,25 @@
       <c r="U11" s="38"/>
       <c r="V11" s="38"/>
       <c r="W11" s="39"/>
-      <c r="X11" s="44"/>
+      <c r="X11" s="42"/>
       <c r="Y11" s="38"/>
       <c r="Z11" s="38"/>
       <c r="AA11" s="38"/>
       <c r="AB11" s="38"/>
       <c r="AC11" s="39"/>
-      <c r="AD11" s="45"/>
+      <c r="AD11" s="43"/>
       <c r="AE11" s="38"/>
       <c r="AF11" s="38"/>
       <c r="AG11" s="39"/>
-      <c r="AH11" s="46" t="s">
+      <c r="AH11" s="44" t="s">
         <v>14</v>
       </c>
       <c r="AI11" s="38"/>
       <c r="AJ11" s="38"/>
       <c r="AK11" s="39"/>
-      <c r="AL11" s="45"/>
+      <c r="AL11" s="43"/>
       <c r="AM11" s="39"/>
-      <c r="AN11" s="46" t="s">
+      <c r="AN11" s="44" t="s">
         <v>14</v>
       </c>
       <c r="AO11" s="39"/>
@@ -1552,12 +1530,12 @@
     </row>
     <row r="12" ht="25.5" customHeight="1">
       <c r="A12" s="9"/>
-      <c r="B12" s="43"/>
+      <c r="B12" s="41"/>
       <c r="C12" s="38"/>
       <c r="D12" s="38"/>
       <c r="E12" s="38"/>
       <c r="F12" s="39"/>
-      <c r="G12" s="47"/>
+      <c r="G12" s="45"/>
       <c r="H12" s="38"/>
       <c r="I12" s="38"/>
       <c r="J12" s="38"/>
@@ -1574,25 +1552,25 @@
       <c r="U12" s="38"/>
       <c r="V12" s="38"/>
       <c r="W12" s="39"/>
-      <c r="X12" s="44"/>
+      <c r="X12" s="42"/>
       <c r="Y12" s="38"/>
       <c r="Z12" s="38"/>
       <c r="AA12" s="38"/>
       <c r="AB12" s="38"/>
       <c r="AC12" s="39"/>
-      <c r="AD12" s="45"/>
+      <c r="AD12" s="43"/>
       <c r="AE12" s="38"/>
       <c r="AF12" s="38"/>
       <c r="AG12" s="39"/>
-      <c r="AH12" s="46" t="s">
+      <c r="AH12" s="44" t="s">
         <v>14</v>
       </c>
       <c r="AI12" s="38"/>
       <c r="AJ12" s="38"/>
       <c r="AK12" s="39"/>
-      <c r="AL12" s="45"/>
+      <c r="AL12" s="43"/>
       <c r="AM12" s="39"/>
-      <c r="AN12" s="46" t="s">
+      <c r="AN12" s="44" t="s">
         <v>14</v>
       </c>
       <c r="AO12" s="39"/>
@@ -1610,12 +1588,12 @@
     </row>
     <row r="13" ht="25.5" customHeight="1">
       <c r="A13" s="9"/>
-      <c r="B13" s="43"/>
+      <c r="B13" s="41"/>
       <c r="C13" s="38"/>
       <c r="D13" s="38"/>
       <c r="E13" s="38"/>
       <c r="F13" s="39"/>
-      <c r="G13" s="47"/>
+      <c r="G13" s="45"/>
       <c r="H13" s="38"/>
       <c r="I13" s="38"/>
       <c r="J13" s="38"/>
@@ -1632,25 +1610,25 @@
       <c r="U13" s="38"/>
       <c r="V13" s="38"/>
       <c r="W13" s="39"/>
-      <c r="X13" s="44"/>
+      <c r="X13" s="42"/>
       <c r="Y13" s="38"/>
       <c r="Z13" s="38"/>
       <c r="AA13" s="38"/>
       <c r="AB13" s="38"/>
       <c r="AC13" s="39"/>
-      <c r="AD13" s="45"/>
+      <c r="AD13" s="43"/>
       <c r="AE13" s="38"/>
       <c r="AF13" s="38"/>
       <c r="AG13" s="39"/>
-      <c r="AH13" s="46" t="s">
+      <c r="AH13" s="44" t="s">
         <v>14</v>
       </c>
       <c r="AI13" s="38"/>
       <c r="AJ13" s="38"/>
       <c r="AK13" s="39"/>
-      <c r="AL13" s="45"/>
+      <c r="AL13" s="43"/>
       <c r="AM13" s="39"/>
-      <c r="AN13" s="46" t="s">
+      <c r="AN13" s="44" t="s">
         <v>14</v>
       </c>
       <c r="AO13" s="39"/>
@@ -1668,12 +1646,12 @@
     </row>
     <row r="14" ht="25.5" customHeight="1">
       <c r="A14" s="9"/>
-      <c r="B14" s="43"/>
+      <c r="B14" s="41"/>
       <c r="C14" s="38"/>
       <c r="D14" s="38"/>
       <c r="E14" s="38"/>
       <c r="F14" s="39"/>
-      <c r="G14" s="47"/>
+      <c r="G14" s="45"/>
       <c r="H14" s="38"/>
       <c r="I14" s="38"/>
       <c r="J14" s="38"/>
@@ -1690,25 +1668,25 @@
       <c r="U14" s="38"/>
       <c r="V14" s="38"/>
       <c r="W14" s="39"/>
-      <c r="X14" s="44"/>
+      <c r="X14" s="42"/>
       <c r="Y14" s="38"/>
       <c r="Z14" s="38"/>
       <c r="AA14" s="38"/>
       <c r="AB14" s="38"/>
       <c r="AC14" s="39"/>
-      <c r="AD14" s="45"/>
+      <c r="AD14" s="43"/>
       <c r="AE14" s="38"/>
       <c r="AF14" s="38"/>
       <c r="AG14" s="39"/>
-      <c r="AH14" s="46" t="s">
+      <c r="AH14" s="44" t="s">
         <v>14</v>
       </c>
       <c r="AI14" s="38"/>
       <c r="AJ14" s="38"/>
       <c r="AK14" s="39"/>
-      <c r="AL14" s="45"/>
+      <c r="AL14" s="43"/>
       <c r="AM14" s="39"/>
-      <c r="AN14" s="46" t="s">
+      <c r="AN14" s="44" t="s">
         <v>14</v>
       </c>
       <c r="AO14" s="39"/>
@@ -1721,17 +1699,17 @@
       <c r="AV14" s="9"/>
       <c r="AW14" s="9"/>
       <c r="AX14" s="9"/>
-      <c r="AY14" s="48"/>
+      <c r="AY14" s="46"/>
       <c r="AZ14" s="9"/>
     </row>
     <row r="15" ht="25.5" customHeight="1">
       <c r="A15" s="9"/>
-      <c r="B15" s="43"/>
+      <c r="B15" s="41"/>
       <c r="C15" s="38"/>
       <c r="D15" s="38"/>
       <c r="E15" s="38"/>
       <c r="F15" s="39"/>
-      <c r="G15" s="47"/>
+      <c r="G15" s="45"/>
       <c r="H15" s="38"/>
       <c r="I15" s="38"/>
       <c r="J15" s="38"/>
@@ -1748,25 +1726,25 @@
       <c r="U15" s="38"/>
       <c r="V15" s="38"/>
       <c r="W15" s="39"/>
-      <c r="X15" s="44"/>
+      <c r="X15" s="42"/>
       <c r="Y15" s="38"/>
       <c r="Z15" s="38"/>
       <c r="AA15" s="38"/>
       <c r="AB15" s="38"/>
       <c r="AC15" s="39"/>
-      <c r="AD15" s="45"/>
+      <c r="AD15" s="43"/>
       <c r="AE15" s="38"/>
       <c r="AF15" s="38"/>
       <c r="AG15" s="39"/>
-      <c r="AH15" s="46" t="s">
+      <c r="AH15" s="44" t="s">
         <v>14</v>
       </c>
       <c r="AI15" s="38"/>
       <c r="AJ15" s="38"/>
       <c r="AK15" s="39"/>
-      <c r="AL15" s="45"/>
+      <c r="AL15" s="43"/>
       <c r="AM15" s="39"/>
-      <c r="AN15" s="46" t="s">
+      <c r="AN15" s="44" t="s">
         <v>14</v>
       </c>
       <c r="AO15" s="39"/>
@@ -1784,12 +1762,12 @@
     </row>
     <row r="16" ht="25.5" customHeight="1">
       <c r="A16" s="9"/>
-      <c r="B16" s="43"/>
+      <c r="B16" s="41"/>
       <c r="C16" s="38"/>
       <c r="D16" s="38"/>
       <c r="E16" s="38"/>
       <c r="F16" s="39"/>
-      <c r="G16" s="47"/>
+      <c r="G16" s="45"/>
       <c r="H16" s="38"/>
       <c r="I16" s="38"/>
       <c r="J16" s="38"/>
@@ -1806,25 +1784,25 @@
       <c r="U16" s="38"/>
       <c r="V16" s="38"/>
       <c r="W16" s="39"/>
-      <c r="X16" s="44"/>
+      <c r="X16" s="42"/>
       <c r="Y16" s="38"/>
       <c r="Z16" s="38"/>
       <c r="AA16" s="38"/>
       <c r="AB16" s="38"/>
       <c r="AC16" s="39"/>
-      <c r="AD16" s="45"/>
+      <c r="AD16" s="43"/>
       <c r="AE16" s="38"/>
       <c r="AF16" s="38"/>
       <c r="AG16" s="39"/>
-      <c r="AH16" s="46" t="s">
+      <c r="AH16" s="44" t="s">
         <v>14</v>
       </c>
       <c r="AI16" s="38"/>
       <c r="AJ16" s="38"/>
       <c r="AK16" s="39"/>
-      <c r="AL16" s="45"/>
+      <c r="AL16" s="43"/>
       <c r="AM16" s="39"/>
-      <c r="AN16" s="46" t="s">
+      <c r="AN16" s="44" t="s">
         <v>14</v>
       </c>
       <c r="AO16" s="39"/>
@@ -1842,12 +1820,12 @@
     </row>
     <row r="17" ht="25.5" customHeight="1">
       <c r="A17" s="9"/>
-      <c r="B17" s="43"/>
+      <c r="B17" s="41"/>
       <c r="C17" s="38"/>
       <c r="D17" s="38"/>
       <c r="E17" s="38"/>
       <c r="F17" s="39"/>
-      <c r="G17" s="47"/>
+      <c r="G17" s="45"/>
       <c r="H17" s="38"/>
       <c r="I17" s="38"/>
       <c r="J17" s="38"/>
@@ -1864,25 +1842,25 @@
       <c r="U17" s="38"/>
       <c r="V17" s="38"/>
       <c r="W17" s="39"/>
-      <c r="X17" s="44"/>
+      <c r="X17" s="42"/>
       <c r="Y17" s="38"/>
       <c r="Z17" s="38"/>
       <c r="AA17" s="38"/>
       <c r="AB17" s="38"/>
       <c r="AC17" s="39"/>
-      <c r="AD17" s="45"/>
+      <c r="AD17" s="43"/>
       <c r="AE17" s="38"/>
       <c r="AF17" s="38"/>
       <c r="AG17" s="39"/>
-      <c r="AH17" s="46" t="s">
+      <c r="AH17" s="44" t="s">
         <v>14</v>
       </c>
       <c r="AI17" s="38"/>
       <c r="AJ17" s="38"/>
       <c r="AK17" s="39"/>
-      <c r="AL17" s="45"/>
+      <c r="AL17" s="43"/>
       <c r="AM17" s="39"/>
-      <c r="AN17" s="46" t="s">
+      <c r="AN17" s="44" t="s">
         <v>14</v>
       </c>
       <c r="AO17" s="39"/>
@@ -1900,12 +1878,12 @@
     </row>
     <row r="18" ht="25.5" customHeight="1">
       <c r="A18" s="9"/>
-      <c r="B18" s="43"/>
+      <c r="B18" s="41"/>
       <c r="C18" s="38"/>
       <c r="D18" s="38"/>
       <c r="E18" s="38"/>
       <c r="F18" s="39"/>
-      <c r="G18" s="47"/>
+      <c r="G18" s="45"/>
       <c r="H18" s="38"/>
       <c r="I18" s="38"/>
       <c r="J18" s="38"/>
@@ -1922,25 +1900,25 @@
       <c r="U18" s="38"/>
       <c r="V18" s="38"/>
       <c r="W18" s="39"/>
-      <c r="X18" s="44"/>
+      <c r="X18" s="42"/>
       <c r="Y18" s="38"/>
       <c r="Z18" s="38"/>
       <c r="AA18" s="38"/>
       <c r="AB18" s="38"/>
       <c r="AC18" s="39"/>
-      <c r="AD18" s="45"/>
+      <c r="AD18" s="43"/>
       <c r="AE18" s="38"/>
       <c r="AF18" s="38"/>
       <c r="AG18" s="39"/>
-      <c r="AH18" s="46" t="s">
+      <c r="AH18" s="44" t="s">
         <v>14</v>
       </c>
       <c r="AI18" s="38"/>
       <c r="AJ18" s="38"/>
       <c r="AK18" s="39"/>
-      <c r="AL18" s="45"/>
+      <c r="AL18" s="43"/>
       <c r="AM18" s="39"/>
-      <c r="AN18" s="46" t="s">
+      <c r="AN18" s="44" t="s">
         <v>14</v>
       </c>
       <c r="AO18" s="39"/>
@@ -1958,12 +1936,12 @@
     </row>
     <row r="19" ht="25.5" customHeight="1">
       <c r="A19" s="9"/>
-      <c r="B19" s="43"/>
+      <c r="B19" s="41"/>
       <c r="C19" s="38"/>
       <c r="D19" s="38"/>
       <c r="E19" s="38"/>
       <c r="F19" s="39"/>
-      <c r="G19" s="47"/>
+      <c r="G19" s="45"/>
       <c r="H19" s="38"/>
       <c r="I19" s="38"/>
       <c r="J19" s="38"/>
@@ -1980,25 +1958,25 @@
       <c r="U19" s="38"/>
       <c r="V19" s="38"/>
       <c r="W19" s="39"/>
-      <c r="X19" s="44"/>
+      <c r="X19" s="42"/>
       <c r="Y19" s="38"/>
       <c r="Z19" s="38"/>
       <c r="AA19" s="38"/>
       <c r="AB19" s="38"/>
       <c r="AC19" s="39"/>
-      <c r="AD19" s="45"/>
+      <c r="AD19" s="43"/>
       <c r="AE19" s="38"/>
       <c r="AF19" s="38"/>
       <c r="AG19" s="39"/>
-      <c r="AH19" s="46" t="s">
+      <c r="AH19" s="44" t="s">
         <v>14</v>
       </c>
       <c r="AI19" s="38"/>
       <c r="AJ19" s="38"/>
       <c r="AK19" s="39"/>
-      <c r="AL19" s="45"/>
+      <c r="AL19" s="43"/>
       <c r="AM19" s="39"/>
-      <c r="AN19" s="46" t="s">
+      <c r="AN19" s="44" t="s">
         <v>14</v>
       </c>
       <c r="AO19" s="39"/>
@@ -2016,12 +1994,12 @@
     </row>
     <row r="20" ht="25.5" customHeight="1">
       <c r="A20" s="9"/>
-      <c r="B20" s="43"/>
+      <c r="B20" s="41"/>
       <c r="C20" s="38"/>
       <c r="D20" s="38"/>
       <c r="E20" s="38"/>
       <c r="F20" s="39"/>
-      <c r="G20" s="47"/>
+      <c r="G20" s="45"/>
       <c r="H20" s="38"/>
       <c r="I20" s="38"/>
       <c r="J20" s="38"/>
@@ -2038,25 +2016,25 @@
       <c r="U20" s="38"/>
       <c r="V20" s="38"/>
       <c r="W20" s="39"/>
-      <c r="X20" s="44"/>
+      <c r="X20" s="42"/>
       <c r="Y20" s="38"/>
       <c r="Z20" s="38"/>
       <c r="AA20" s="38"/>
       <c r="AB20" s="38"/>
       <c r="AC20" s="39"/>
-      <c r="AD20" s="45"/>
+      <c r="AD20" s="43"/>
       <c r="AE20" s="38"/>
       <c r="AF20" s="38"/>
       <c r="AG20" s="39"/>
-      <c r="AH20" s="46" t="s">
+      <c r="AH20" s="44" t="s">
         <v>14</v>
       </c>
       <c r="AI20" s="38"/>
       <c r="AJ20" s="38"/>
       <c r="AK20" s="39"/>
-      <c r="AL20" s="45"/>
+      <c r="AL20" s="43"/>
       <c r="AM20" s="39"/>
-      <c r="AN20" s="46" t="s">
+      <c r="AN20" s="44" t="s">
         <v>14</v>
       </c>
       <c r="AO20" s="39"/>
@@ -2074,12 +2052,12 @@
     </row>
     <row r="21" ht="25.5" customHeight="1">
       <c r="A21" s="9"/>
-      <c r="B21" s="43"/>
+      <c r="B21" s="41"/>
       <c r="C21" s="38"/>
       <c r="D21" s="38"/>
       <c r="E21" s="38"/>
       <c r="F21" s="39"/>
-      <c r="G21" s="47"/>
+      <c r="G21" s="45"/>
       <c r="H21" s="38"/>
       <c r="I21" s="38"/>
       <c r="J21" s="38"/>
@@ -2096,25 +2074,25 @@
       <c r="U21" s="38"/>
       <c r="V21" s="38"/>
       <c r="W21" s="39"/>
-      <c r="X21" s="44"/>
+      <c r="X21" s="42"/>
       <c r="Y21" s="38"/>
       <c r="Z21" s="38"/>
       <c r="AA21" s="38"/>
       <c r="AB21" s="38"/>
       <c r="AC21" s="39"/>
-      <c r="AD21" s="45"/>
+      <c r="AD21" s="43"/>
       <c r="AE21" s="38"/>
       <c r="AF21" s="38"/>
       <c r="AG21" s="39"/>
-      <c r="AH21" s="46" t="s">
+      <c r="AH21" s="44" t="s">
         <v>14</v>
       </c>
       <c r="AI21" s="38"/>
       <c r="AJ21" s="38"/>
       <c r="AK21" s="39"/>
-      <c r="AL21" s="45"/>
+      <c r="AL21" s="43"/>
       <c r="AM21" s="39"/>
-      <c r="AN21" s="46" t="s">
+      <c r="AN21" s="44" t="s">
         <v>14</v>
       </c>
       <c r="AO21" s="39"/>
@@ -2132,12 +2110,12 @@
     </row>
     <row r="22" ht="25.5" customHeight="1">
       <c r="A22" s="9"/>
-      <c r="B22" s="43"/>
+      <c r="B22" s="41"/>
       <c r="C22" s="38"/>
       <c r="D22" s="38"/>
       <c r="E22" s="38"/>
       <c r="F22" s="39"/>
-      <c r="G22" s="47"/>
+      <c r="G22" s="45"/>
       <c r="H22" s="38"/>
       <c r="I22" s="38"/>
       <c r="J22" s="38"/>
@@ -2154,25 +2132,25 @@
       <c r="U22" s="38"/>
       <c r="V22" s="38"/>
       <c r="W22" s="39"/>
-      <c r="X22" s="44"/>
+      <c r="X22" s="42"/>
       <c r="Y22" s="38"/>
       <c r="Z22" s="38"/>
       <c r="AA22" s="38"/>
       <c r="AB22" s="38"/>
       <c r="AC22" s="39"/>
-      <c r="AD22" s="45"/>
+      <c r="AD22" s="43"/>
       <c r="AE22" s="38"/>
       <c r="AF22" s="38"/>
       <c r="AG22" s="39"/>
-      <c r="AH22" s="46" t="s">
+      <c r="AH22" s="44" t="s">
         <v>14</v>
       </c>
       <c r="AI22" s="38"/>
       <c r="AJ22" s="38"/>
       <c r="AK22" s="39"/>
-      <c r="AL22" s="45"/>
+      <c r="AL22" s="43"/>
       <c r="AM22" s="39"/>
-      <c r="AN22" s="46" t="s">
+      <c r="AN22" s="44" t="s">
         <v>14</v>
       </c>
       <c r="AO22" s="39"/>
@@ -2190,12 +2168,12 @@
     </row>
     <row r="23" ht="27.75" customHeight="1">
       <c r="A23" s="9"/>
-      <c r="B23" s="43"/>
+      <c r="B23" s="41"/>
       <c r="C23" s="38"/>
       <c r="D23" s="38"/>
       <c r="E23" s="38"/>
       <c r="F23" s="39"/>
-      <c r="G23" s="47"/>
+      <c r="G23" s="45"/>
       <c r="H23" s="38"/>
       <c r="I23" s="38"/>
       <c r="J23" s="38"/>
@@ -2212,25 +2190,25 @@
       <c r="U23" s="38"/>
       <c r="V23" s="38"/>
       <c r="W23" s="39"/>
-      <c r="X23" s="44"/>
+      <c r="X23" s="42"/>
       <c r="Y23" s="38"/>
       <c r="Z23" s="38"/>
       <c r="AA23" s="38"/>
       <c r="AB23" s="38"/>
       <c r="AC23" s="39"/>
-      <c r="AD23" s="45"/>
+      <c r="AD23" s="43"/>
       <c r="AE23" s="38"/>
       <c r="AF23" s="38"/>
       <c r="AG23" s="39"/>
-      <c r="AH23" s="46" t="s">
+      <c r="AH23" s="44" t="s">
         <v>14</v>
       </c>
       <c r="AI23" s="38"/>
       <c r="AJ23" s="38"/>
       <c r="AK23" s="39"/>
-      <c r="AL23" s="45"/>
+      <c r="AL23" s="43"/>
       <c r="AM23" s="39"/>
-      <c r="AN23" s="46" t="s">
+      <c r="AN23" s="44" t="s">
         <v>14</v>
       </c>
       <c r="AO23" s="39"/>
@@ -2248,12 +2226,12 @@
     </row>
     <row r="24" ht="27.75" customHeight="1">
       <c r="A24" s="9"/>
-      <c r="B24" s="43"/>
+      <c r="B24" s="41"/>
       <c r="C24" s="38"/>
       <c r="D24" s="38"/>
       <c r="E24" s="38"/>
       <c r="F24" s="39"/>
-      <c r="G24" s="47"/>
+      <c r="G24" s="45"/>
       <c r="H24" s="38"/>
       <c r="I24" s="38"/>
       <c r="J24" s="38"/>
@@ -2270,25 +2248,25 @@
       <c r="U24" s="38"/>
       <c r="V24" s="38"/>
       <c r="W24" s="39"/>
-      <c r="X24" s="44"/>
+      <c r="X24" s="42"/>
       <c r="Y24" s="38"/>
       <c r="Z24" s="38"/>
       <c r="AA24" s="38"/>
       <c r="AB24" s="38"/>
       <c r="AC24" s="39"/>
-      <c r="AD24" s="45"/>
+      <c r="AD24" s="43"/>
       <c r="AE24" s="38"/>
       <c r="AF24" s="38"/>
       <c r="AG24" s="39"/>
-      <c r="AH24" s="46" t="s">
+      <c r="AH24" s="44" t="s">
         <v>14</v>
       </c>
       <c r="AI24" s="38"/>
       <c r="AJ24" s="38"/>
       <c r="AK24" s="39"/>
-      <c r="AL24" s="45"/>
+      <c r="AL24" s="43"/>
       <c r="AM24" s="39"/>
-      <c r="AN24" s="46" t="s">
+      <c r="AN24" s="44" t="s">
         <v>14</v>
       </c>
       <c r="AO24" s="39"/>
@@ -2306,12 +2284,12 @@
     </row>
     <row r="25" ht="27.75" customHeight="1">
       <c r="A25" s="9"/>
-      <c r="B25" s="43"/>
+      <c r="B25" s="41"/>
       <c r="C25" s="38"/>
       <c r="D25" s="38"/>
       <c r="E25" s="38"/>
       <c r="F25" s="39"/>
-      <c r="G25" s="47"/>
+      <c r="G25" s="45"/>
       <c r="H25" s="38"/>
       <c r="I25" s="38"/>
       <c r="J25" s="38"/>
@@ -2328,25 +2306,25 @@
       <c r="U25" s="38"/>
       <c r="V25" s="38"/>
       <c r="W25" s="39"/>
-      <c r="X25" s="44"/>
+      <c r="X25" s="42"/>
       <c r="Y25" s="38"/>
       <c r="Z25" s="38"/>
       <c r="AA25" s="38"/>
       <c r="AB25" s="38"/>
       <c r="AC25" s="39"/>
-      <c r="AD25" s="45"/>
+      <c r="AD25" s="43"/>
       <c r="AE25" s="38"/>
       <c r="AF25" s="38"/>
       <c r="AG25" s="39"/>
-      <c r="AH25" s="46" t="s">
+      <c r="AH25" s="44" t="s">
         <v>14</v>
       </c>
       <c r="AI25" s="38"/>
       <c r="AJ25" s="38"/>
       <c r="AK25" s="39"/>
-      <c r="AL25" s="45"/>
+      <c r="AL25" s="43"/>
       <c r="AM25" s="39"/>
-      <c r="AN25" s="46" t="s">
+      <c r="AN25" s="44" t="s">
         <v>14</v>
       </c>
       <c r="AO25" s="39"/>
@@ -2364,12 +2342,12 @@
     </row>
     <row r="26" ht="27.75" customHeight="1">
       <c r="A26" s="9"/>
-      <c r="B26" s="43"/>
+      <c r="B26" s="41"/>
       <c r="C26" s="38"/>
       <c r="D26" s="38"/>
       <c r="E26" s="38"/>
       <c r="F26" s="39"/>
-      <c r="G26" s="47"/>
+      <c r="G26" s="45"/>
       <c r="H26" s="38"/>
       <c r="I26" s="38"/>
       <c r="J26" s="38"/>
@@ -2386,25 +2364,25 @@
       <c r="U26" s="38"/>
       <c r="V26" s="38"/>
       <c r="W26" s="39"/>
-      <c r="X26" s="44"/>
+      <c r="X26" s="42"/>
       <c r="Y26" s="38"/>
       <c r="Z26" s="38"/>
       <c r="AA26" s="38"/>
       <c r="AB26" s="38"/>
       <c r="AC26" s="39"/>
-      <c r="AD26" s="45"/>
+      <c r="AD26" s="43"/>
       <c r="AE26" s="38"/>
       <c r="AF26" s="38"/>
       <c r="AG26" s="39"/>
-      <c r="AH26" s="46" t="s">
+      <c r="AH26" s="44" t="s">
         <v>14</v>
       </c>
       <c r="AI26" s="38"/>
       <c r="AJ26" s="38"/>
       <c r="AK26" s="39"/>
-      <c r="AL26" s="45"/>
+      <c r="AL26" s="43"/>
       <c r="AM26" s="39"/>
-      <c r="AN26" s="46" t="s">
+      <c r="AN26" s="44" t="s">
         <v>14</v>
       </c>
       <c r="AO26" s="39"/>
@@ -2422,12 +2400,12 @@
     </row>
     <row r="27" ht="27.75" customHeight="1">
       <c r="A27" s="9"/>
-      <c r="B27" s="43"/>
+      <c r="B27" s="41"/>
       <c r="C27" s="38"/>
       <c r="D27" s="38"/>
       <c r="E27" s="38"/>
       <c r="F27" s="39"/>
-      <c r="G27" s="47"/>
+      <c r="G27" s="45"/>
       <c r="H27" s="38"/>
       <c r="I27" s="38"/>
       <c r="J27" s="38"/>
@@ -2444,25 +2422,25 @@
       <c r="U27" s="38"/>
       <c r="V27" s="38"/>
       <c r="W27" s="39"/>
-      <c r="X27" s="44"/>
+      <c r="X27" s="42"/>
       <c r="Y27" s="38"/>
       <c r="Z27" s="38"/>
       <c r="AA27" s="38"/>
       <c r="AB27" s="38"/>
       <c r="AC27" s="39"/>
-      <c r="AD27" s="45"/>
+      <c r="AD27" s="43"/>
       <c r="AE27" s="38"/>
       <c r="AF27" s="38"/>
       <c r="AG27" s="39"/>
-      <c r="AH27" s="46" t="s">
+      <c r="AH27" s="44" t="s">
         <v>14</v>
       </c>
       <c r="AI27" s="38"/>
       <c r="AJ27" s="38"/>
       <c r="AK27" s="39"/>
-      <c r="AL27" s="45"/>
+      <c r="AL27" s="43"/>
       <c r="AM27" s="39"/>
-      <c r="AN27" s="46" t="s">
+      <c r="AN27" s="44" t="s">
         <v>14</v>
       </c>
       <c r="AO27" s="39"/>
@@ -2480,12 +2458,12 @@
     </row>
     <row r="28" ht="27.75" customHeight="1">
       <c r="A28" s="9"/>
-      <c r="B28" s="43"/>
+      <c r="B28" s="41"/>
       <c r="C28" s="38"/>
       <c r="D28" s="38"/>
       <c r="E28" s="38"/>
       <c r="F28" s="39"/>
-      <c r="G28" s="47"/>
+      <c r="G28" s="45"/>
       <c r="H28" s="38"/>
       <c r="I28" s="38"/>
       <c r="J28" s="38"/>
@@ -2502,25 +2480,25 @@
       <c r="U28" s="38"/>
       <c r="V28" s="38"/>
       <c r="W28" s="39"/>
-      <c r="X28" s="44"/>
+      <c r="X28" s="42"/>
       <c r="Y28" s="38"/>
       <c r="Z28" s="38"/>
       <c r="AA28" s="38"/>
       <c r="AB28" s="38"/>
       <c r="AC28" s="39"/>
-      <c r="AD28" s="45"/>
+      <c r="AD28" s="43"/>
       <c r="AE28" s="38"/>
       <c r="AF28" s="38"/>
       <c r="AG28" s="39"/>
-      <c r="AH28" s="46" t="s">
+      <c r="AH28" s="44" t="s">
         <v>14</v>
       </c>
       <c r="AI28" s="38"/>
       <c r="AJ28" s="38"/>
       <c r="AK28" s="39"/>
-      <c r="AL28" s="45"/>
+      <c r="AL28" s="43"/>
       <c r="AM28" s="39"/>
-      <c r="AN28" s="46" t="s">
+      <c r="AN28" s="44" t="s">
         <v>14</v>
       </c>
       <c r="AO28" s="39"/>
@@ -2538,12 +2516,12 @@
     </row>
     <row r="29" ht="27.75" customHeight="1">
       <c r="A29" s="9"/>
-      <c r="B29" s="43"/>
+      <c r="B29" s="41"/>
       <c r="C29" s="38"/>
       <c r="D29" s="38"/>
       <c r="E29" s="38"/>
       <c r="F29" s="39"/>
-      <c r="G29" s="47"/>
+      <c r="G29" s="45"/>
       <c r="H29" s="38"/>
       <c r="I29" s="38"/>
       <c r="J29" s="38"/>
@@ -2560,25 +2538,25 @@
       <c r="U29" s="38"/>
       <c r="V29" s="38"/>
       <c r="W29" s="39"/>
-      <c r="X29" s="44"/>
+      <c r="X29" s="42"/>
       <c r="Y29" s="38"/>
       <c r="Z29" s="38"/>
       <c r="AA29" s="38"/>
       <c r="AB29" s="38"/>
       <c r="AC29" s="39"/>
-      <c r="AD29" s="45"/>
+      <c r="AD29" s="43"/>
       <c r="AE29" s="38"/>
       <c r="AF29" s="38"/>
       <c r="AG29" s="39"/>
-      <c r="AH29" s="46" t="s">
+      <c r="AH29" s="44" t="s">
         <v>14</v>
       </c>
       <c r="AI29" s="38"/>
       <c r="AJ29" s="38"/>
       <c r="AK29" s="39"/>
-      <c r="AL29" s="45"/>
+      <c r="AL29" s="43"/>
       <c r="AM29" s="39"/>
-      <c r="AN29" s="46" t="s">
+      <c r="AN29" s="44" t="s">
         <v>14</v>
       </c>
       <c r="AO29" s="39"/>
@@ -2596,7 +2574,7 @@
     </row>
     <row r="30" ht="27.75" customHeight="1">
       <c r="A30" s="9"/>
-      <c r="B30" s="49" t="s">
+      <c r="B30" s="47" t="s">
         <v>15</v>
       </c>
       <c r="C30" s="27"/>
@@ -2652,7 +2630,7 @@
     </row>
     <row r="31" ht="27.75" customHeight="1">
       <c r="A31" s="9"/>
-      <c r="B31" s="49" t="s">
+      <c r="B31" s="47" t="s">
         <v>16</v>
       </c>
       <c r="C31" s="27"/>
@@ -2682,7 +2660,7 @@
       <c r="AA31" s="9"/>
       <c r="AB31" s="9"/>
       <c r="AC31" s="9"/>
-      <c r="AD31" s="50" t="s">
+      <c r="AD31" s="48" t="s">
         <v>17</v>
       </c>
       <c r="AE31" s="27"/>
@@ -2709,48 +2687,48 @@
       <c r="AZ31" s="9"/>
     </row>
     <row r="32" ht="27.75" customHeight="1">
-      <c r="A32" s="51"/>
-      <c r="B32" s="52"/>
-      <c r="C32" s="52"/>
-      <c r="D32" s="52"/>
-      <c r="E32" s="52"/>
-      <c r="F32" s="52"/>
-      <c r="G32" s="52"/>
-      <c r="H32" s="52"/>
-      <c r="I32" s="52"/>
-      <c r="J32" s="52"/>
-      <c r="K32" s="52"/>
-      <c r="L32" s="52"/>
-      <c r="M32" s="52"/>
-      <c r="N32" s="52"/>
-      <c r="O32" s="52"/>
-      <c r="P32" s="52"/>
-      <c r="Q32" s="52"/>
-      <c r="R32" s="52"/>
-      <c r="S32" s="52"/>
-      <c r="T32" s="52"/>
-      <c r="U32" s="52"/>
-      <c r="V32" s="52"/>
-      <c r="W32" s="52"/>
-      <c r="X32" s="52"/>
-      <c r="Y32" s="52"/>
-      <c r="Z32" s="52"/>
-      <c r="AA32" s="52"/>
-      <c r="AB32" s="52"/>
-      <c r="AC32" s="52"/>
-      <c r="AD32" s="52"/>
-      <c r="AE32" s="52"/>
-      <c r="AF32" s="52"/>
-      <c r="AG32" s="52"/>
-      <c r="AH32" s="52"/>
-      <c r="AI32" s="52"/>
-      <c r="AJ32" s="52"/>
-      <c r="AK32" s="52"/>
-      <c r="AL32" s="52"/>
-      <c r="AM32" s="52"/>
-      <c r="AN32" s="52"/>
-      <c r="AO32" s="52"/>
-      <c r="AP32" s="53"/>
+      <c r="A32" s="49"/>
+      <c r="B32" s="50"/>
+      <c r="C32" s="50"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
+      <c r="F32" s="50"/>
+      <c r="G32" s="50"/>
+      <c r="H32" s="50"/>
+      <c r="I32" s="50"/>
+      <c r="J32" s="50"/>
+      <c r="K32" s="50"/>
+      <c r="L32" s="50"/>
+      <c r="M32" s="50"/>
+      <c r="N32" s="50"/>
+      <c r="O32" s="50"/>
+      <c r="P32" s="50"/>
+      <c r="Q32" s="50"/>
+      <c r="R32" s="50"/>
+      <c r="S32" s="50"/>
+      <c r="T32" s="50"/>
+      <c r="U32" s="50"/>
+      <c r="V32" s="50"/>
+      <c r="W32" s="50"/>
+      <c r="X32" s="50"/>
+      <c r="Y32" s="50"/>
+      <c r="Z32" s="50"/>
+      <c r="AA32" s="50"/>
+      <c r="AB32" s="50"/>
+      <c r="AC32" s="50"/>
+      <c r="AD32" s="50"/>
+      <c r="AE32" s="50"/>
+      <c r="AF32" s="50"/>
+      <c r="AG32" s="50"/>
+      <c r="AH32" s="50"/>
+      <c r="AI32" s="50"/>
+      <c r="AJ32" s="50"/>
+      <c r="AK32" s="50"/>
+      <c r="AL32" s="50"/>
+      <c r="AM32" s="50"/>
+      <c r="AN32" s="50"/>
+      <c r="AO32" s="50"/>
+      <c r="AP32" s="51"/>
       <c r="AQ32" s="9"/>
       <c r="AR32" s="9"/>
       <c r="AS32" s="9"/>
@@ -2883,7 +2861,7 @@
       <c r="J35" s="9"/>
       <c r="K35" s="9"/>
       <c r="L35" s="9"/>
-      <c r="M35" s="54"/>
+      <c r="M35" s="52"/>
       <c r="N35" s="9"/>
       <c r="O35" s="9"/>
       <c r="P35" s="9"/>

--- a/modelo_op_solda.xlsx
+++ b/modelo_op_solda.xlsx
@@ -23,8 +23,8 @@
 Página</t>
   </si>
   <si>
-    <t>RQ PCP-016-000
-02/01/2024
+    <t>RQ PCP-030-000
+22/04/2025
 -
 N/A</t>
   </si>
@@ -510,7 +510,7 @@
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="6" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
